--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/4138-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/4138-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{43AC9DCE-23CE-4BCA-A11B-7EDB26AEC1CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{56EE31EC-EA9E-4581-AA4C-D639B766A450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{086F78CD-9A8A-47CD-BFD0-278119F5F53E}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{937A35BE-B670-408B-8888-6F69DD0F5F45}"/>
   </bookViews>
   <sheets>
     <sheet name="4138-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1541,27 +1541,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2156086-9A43-4117-88AF-56058DE179BF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F595B832-9EC6-4C5F-B8A1-82166BD3D9AC}">
   <dimension ref="A1:X25"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.375" customWidth="1"/>
-    <col min="3" max="3" width="10.25" customWidth="1"/>
-    <col min="4" max="4" width="6.625" customWidth="1"/>
-    <col min="5" max="5" width="6.25" customWidth="1"/>
-    <col min="6" max="6" width="6.625" customWidth="1"/>
-    <col min="7" max="9" width="6.25" customWidth="1"/>
-    <col min="10" max="10" width="6.625" customWidth="1"/>
-    <col min="11" max="13" width="6.25" customWidth="1"/>
-    <col min="14" max="15" width="6.625" customWidth="1"/>
-    <col min="16" max="20" width="6.25" customWidth="1"/>
-    <col min="21" max="21" width="6.625" customWidth="1"/>
-    <col min="22" max="22" width="6.25" customWidth="1"/>
-    <col min="23" max="23" width="6.625" customWidth="1"/>
-    <col min="24" max="24" width="8.25" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1595,7 +1594,7 @@
       <c r="W1" s="31"/>
       <c r="X1" s="23"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1631,7 +1630,7 @@
       <c r="W2" s="33"/>
       <c r="X2" s="34"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1683,7 +1682,7 @@
       </c>
       <c r="X3" s="37"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1751,7 +1750,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="38">
         <v>2024</v>
       </c>
@@ -1823,7 +1822,7 @@
         <v>8.61</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="40"/>
       <c r="B6" s="41"/>
       <c r="C6" s="13" t="s">
@@ -1851,7 +1850,7 @@
       <c r="W6" s="47"/>
       <c r="X6" s="43"/>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="48">
         <v>2023</v>
       </c>
@@ -1923,7 +1922,7 @@
         <v>8.73</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="50"/>
       <c r="B8" s="51"/>
       <c r="C8" s="16" t="s">
@@ -1951,7 +1950,7 @@
       <c r="W8" s="57"/>
       <c r="X8" s="53"/>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="38">
         <v>2022</v>
       </c>
@@ -2023,7 +2022,7 @@
         <v>6.68</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="40"/>
       <c r="B10" s="41"/>
       <c r="C10" s="13" t="s">
@@ -2051,7 +2050,7 @@
       <c r="W10" s="47"/>
       <c r="X10" s="43"/>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="58">
         <v>2021</v>
       </c>
@@ -2123,7 +2122,7 @@
         <v>7.07</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="60">
         <v>2020</v>
       </c>
@@ -2195,7 +2194,7 @@
         <v>7.22</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="58">
         <v>2019</v>
       </c>
@@ -2267,7 +2266,7 @@
         <v>8.35</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="60">
         <v>2018</v>
       </c>
@@ -2339,7 +2338,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="58">
         <v>2017</v>
       </c>
@@ -2411,7 +2410,7 @@
         <v>7.56</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="60">
         <v>2016</v>
       </c>
@@ -2483,7 +2482,7 @@
         <v>7.14</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="58">
         <v>2015</v>
       </c>
@@ -2555,7 +2554,7 @@
         <v>7.42</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="60">
         <v>2014</v>
       </c>
@@ -2627,7 +2626,7 @@
         <v>7.88</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="58">
         <v>2013</v>
       </c>
@@ -2699,7 +2698,7 @@
         <v>2.27</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="60">
         <v>2012</v>
       </c>
@@ -2771,7 +2770,7 @@
         <v>6.42</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="58">
         <v>2011</v>
       </c>
@@ -2843,7 +2842,7 @@
         <v>6.66</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="60">
         <v>2010</v>
       </c>
@@ -2915,7 +2914,7 @@
         <v>6.33</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="58">
         <v>2009</v>
       </c>
@@ -2987,7 +2986,7 @@
         <v>3.92</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="60">
         <v>2008</v>
       </c>
@@ -3059,7 +3058,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="58" t="s">
         <v>48</v>
       </c>
